--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487696_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487696_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9214</v>
+        <v>2.3274</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9453</v>
+        <v>1.106</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9761</v>
+        <v>1.2214</v>
       </c>
       <c r="G2" t="n">
         <v>2.7739</v>
@@ -610,13 +610,13 @@
         <v>2.3284</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5704</v>
+        <v>-1.1645</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2719</v>
+        <v>-1.1112</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2985</v>
+        <v>-0.0532</v>
       </c>
       <c r="V2" t="n">
         <v>0.3299</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2257</v>
+        <v>0.3135</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5908</v>
+        <v>-0.5302</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8165</v>
+        <v>0.8438</v>
       </c>
       <c r="G3" t="n">
         <v>2.147</v>
@@ -688,13 +688,13 @@
         <v>2.5224</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0855</v>
+        <v>-0.9976</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2113</v>
+        <v>-1.1508</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1259</v>
+        <v>0.1531</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2239</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. SANZ CÁMARA</t>
+          <t>J. TRUJILLO FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1331</v>
+        <v>-0.075</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.2013</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7989000000000001</v>
+        <v>-0.2763</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6274</v>
+        <v>0.4157</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7697</v>
+        <v>-0.8255</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1423</v>
+        <v>1.2413</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6795</v>
+        <v>1.3459</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2656</v>
+        <v>0.0824</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5861</v>
+        <v>1.2635</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0521</v>
+        <v>-0.9302</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.496</v>
+        <v>-0.9079</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5561</v>
+        <v>-0.0223</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3881</v>
+        <v>0.194</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7877999999999999</v>
+        <v>-0.6847</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1346</v>
+        <v>-0.1744</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6532</v>
+        <v>-0.5103</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.894</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1761</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. DEL VALLE REGALADO</t>
+          <t>M. SANZ CÁMARA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3523</v>
+        <v>-0.3575</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2919</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9396</v>
+        <v>-1.2894</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1483</v>
+        <v>0.6274</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0587</v>
+        <v>1.7697</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9104</v>
+        <v>-1.1423</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8895999999999999</v>
+        <v>1.6795</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3718</v>
+        <v>2.2656</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4821</v>
+        <v>-0.5861</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7413</v>
+        <v>-1.0521</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3131</v>
+        <v>-0.496</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4282</v>
+        <v>-0.5561</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3582</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3284</v>
+        <v>0.7761</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3528</v>
+        <v>0.2972</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2113</v>
+        <v>0.1346</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8585</v>
+        <v>0.1626</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.506</v>
+        <v>-0.894</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.506</v>
+        <v>-1.1761</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. RUEDA ALVAREZ</t>
+          <t>M. DEL VALLE REGALADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8161</v>
+        <v>-0.7823</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1436</v>
+        <v>-1.2313</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3275</v>
+        <v>0.449</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1541</v>
+        <v>0.1483</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0206</v>
+        <v>1.0587</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1335</v>
+        <v>-0.9104</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0206</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0206</v>
+        <v>1.3718</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.4821</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1335</v>
+        <v>-0.7413</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.3131</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1335</v>
+        <v>-0.4282</v>
       </c>
       <c r="P6" t="n">
+        <v>1.3582</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-1.1642</v>
-      </c>
       <c r="R6" t="n">
-        <v>0.194</v>
+        <v>2.3284</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.7828000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-1.1508</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.3679</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. TRUJILLO FERNÁNDEZ</t>
+          <t>D. RUEDA ALVAREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8935999999999999</v>
+        <v>-0.8161</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3993</v>
+        <v>-1.1436</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4943</v>
+        <v>0.3275</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4157</v>
+        <v>0.1541</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8255</v>
+        <v>0.0206</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2413</v>
+        <v>0.1335</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3459</v>
+        <v>0.0206</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0824</v>
+        <v>0.0206</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2635</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9302</v>
+        <v>0.1335</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9079</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0223</v>
+        <v>0.1335</v>
       </c>
       <c r="P7" t="n">
+        <v>-0.9702</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1.1642</v>
+      </c>
+      <c r="R7" t="n">
         <v>0.194</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-0.9702</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.1642</v>
-      </c>
       <c r="S7" t="n">
-        <v>-1.5034</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.775</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7282999999999999</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.226</v>
+        <v>-1.117</v>
       </c>
       <c r="E8" t="n">
         <v>1.1474</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3734</v>
+        <v>-2.2644</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9273</v>
@@ -1078,13 +1078,13 @@
         <v>0.7761</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1449</v>
+        <v>-0.0359</v>
       </c>
       <c r="T8" t="n">
         <v>0.2557</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4006</v>
+        <v>-0.2916</v>
       </c>
       <c r="V8" t="n">
         <v>0.2343</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. BATLLE BERNARDO</t>
+          <t>C. BARROS CONDES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6515</v>
+        <v>-2.062</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.5546</v>
+        <v>-0.2766</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9031</v>
+        <v>-1.7855</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.9227</v>
+        <v>-1.081</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0051</v>
+        <v>-2.0325</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.9278</v>
+        <v>0.9515</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.1204</v>
+        <v>-0.0898</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1122</v>
+        <v>-1.3305</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.2326</v>
+        <v>1.2407</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8023</v>
+        <v>-0.9912</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1071</v>
+        <v>-0.7019</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6952</v>
+        <v>-0.2892</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7761</v>
+        <v>0.7761</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9105</v>
+        <v>-0.194</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1344</v>
+        <v>0.9702</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7885</v>
+        <v>-0.2512</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0296</v>
+        <v>0.0073</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2412</v>
+        <v>-0.2585</v>
       </c>
       <c r="V9" t="n">
-        <v>1.8358</v>
+        <v>-1.506</v>
       </c>
       <c r="W9" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3299</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. BARROS CONDES</t>
+          <t>J. AYALA AYLLÓN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6899</v>
+        <v>-2.1952</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8772</v>
+        <v>-0.9817</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8127</v>
+        <v>-1.2136</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.081</v>
+        <v>0.2859</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0325</v>
+        <v>1.7301</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9515</v>
+        <v>-1.4442</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0898</v>
+        <v>1.0997</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3305</v>
+        <v>2.2492</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2407</v>
+        <v>-1.1495</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9912</v>
+        <v>-0.8138</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7019</v>
+        <v>-0.5191</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2892</v>
+        <v>-0.2948</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7761</v>
+        <v>1.3582</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9702</v>
+        <v>2.3284</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8791</v>
+        <v>-1.3916</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5933</v>
+        <v>-1.1112</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2858</v>
+        <v>-0.2804</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.506</v>
+        <v>-2.4477</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.506</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. AYALA AYLLÓN</t>
+          <t>M. BATLLE BERNARDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.792</v>
+        <v>-2.5909</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1423</v>
+        <v>-4.494</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6496</v>
+        <v>1.9031</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2859</v>
+        <v>-2.9227</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7301</v>
+        <v>1.0051</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4442</v>
+        <v>-3.9278</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0997</v>
+        <v>-2.1204</v>
       </c>
       <c r="K11" t="n">
-        <v>2.2492</v>
+        <v>1.1122</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1495</v>
+        <v>-3.2326</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8138</v>
+        <v>-0.8023</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5191</v>
+        <v>-0.1071</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2948</v>
+        <v>-0.6952</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3582</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3284</v>
+        <v>2.1344</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.9883</v>
+        <v>-0.7279</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2719</v>
+        <v>-0.9691</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7164</v>
+        <v>0.2412</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4477</v>
+        <v>1.8358</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4477</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8367</v>
+        <v>-6.3199</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5992</v>
+        <v>-5.0006</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2376</v>
+        <v>-1.3193</v>
       </c>
       <c r="G12" t="n">
         <v>-6.3204</v>
@@ -1390,13 +1390,13 @@
         <v>0.9702</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7658</v>
+        <v>0.2826</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9549</v>
+        <v>0.5535</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1891</v>
+        <v>-0.2708</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2821</v>
@@ -1423,28 +1423,28 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.9779</v>
+        <v>-13.675</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.5742</v>
+        <v>-10.2713</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.4037</v>
+        <v>-3.403700000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.6991</v>
+        <v>-4.699100000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.3367</v>
+        <v>-3.336700000000001</v>
       </c>
       <c r="I13" t="n">
         <v>-1.3624</v>
       </c>
       <c r="J13" t="n">
-        <v>3.963299999999998</v>
+        <v>3.963300000000002</v>
       </c>
       <c r="K13" t="n">
-        <v>1.738500000000001</v>
+        <v>1.7385</v>
       </c>
       <c r="L13" t="n">
         <v>2.2247</v>
@@ -1468,13 +1468,13 @@
         <v>16.4928</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.7593</v>
+        <v>-5.456399999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.0191</v>
+        <v>-4.716400000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7398999999999998</v>
+        <v>-0.74</v>
       </c>
       <c r="V13" t="n">
         <v>-5.4597</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>D. LORENZO  NEGRETE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7935</v>
+        <v>6.0703</v>
       </c>
       <c r="E14" t="n">
-        <v>5.7763</v>
+        <v>5.1764</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0172</v>
+        <v>0.8939</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.1146</v>
+        <v>2.6176</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8544</v>
+        <v>3.0236</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2603</v>
+        <v>-0.406</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.0693</v>
+        <v>3.9824</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.2317</v>
+        <v>3.9546</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1624</v>
+        <v>0.0279</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0454</v>
+        <v>-1.3648</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3773</v>
+        <v>-0.931</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4227</v>
+        <v>-0.4338</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9403</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.1344</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9403</v>
+        <v>1.7463</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5843</v>
+        <v>0.9034</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6099</v>
+        <v>-0.2956</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9745</v>
+        <v>1.199</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3836</v>
+        <v>2.9373</v>
       </c>
       <c r="W14" t="n">
-        <v>4.2358</v>
+        <v>3.6238</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.8522</v>
+        <v>-0.6866</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. LORENZO  NEGRETE</t>
+          <t>V. ALONSO PASCUAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1182</v>
+        <v>3.884</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5758</v>
+        <v>1.1016</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5424</v>
+        <v>2.7823</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6176</v>
+        <v>3.3291</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0236</v>
+        <v>1.5423</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.406</v>
+        <v>1.7868</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9824</v>
+        <v>2.7131</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9546</v>
+        <v>1.31</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0279</v>
+        <v>1.4031</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3648</v>
+        <v>0.616</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.931</v>
+        <v>0.2323</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4338</v>
+        <v>0.3837</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3881</v>
+        <v>-0.194</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.1344</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7463</v>
+        <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0487</v>
+        <v>0.4669</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8962</v>
+        <v>0.2408</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8475</v>
+        <v>0.226</v>
       </c>
       <c r="V15" t="n">
-        <v>2.9373</v>
+        <v>0.2821</v>
       </c>
       <c r="W15" t="n">
-        <v>3.6238</v>
+        <v>0.2821</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6866</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. ALONSO PASCUAL</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2294</v>
+        <v>3.7921</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8013</v>
+        <v>4.0747</v>
       </c>
       <c r="F16" t="n">
-        <v>2.428</v>
+        <v>-0.2826</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3291</v>
+        <v>-1.1146</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5423</v>
+        <v>-0.8544</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7868</v>
+        <v>-0.2603</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7131</v>
+        <v>-1.0693</v>
       </c>
       <c r="K16" t="n">
-        <v>1.31</v>
+        <v>-1.2317</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4031</v>
+        <v>0.1624</v>
       </c>
       <c r="M16" t="n">
-        <v>0.616</v>
+        <v>-0.0454</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2323</v>
+        <v>0.3773</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3837</v>
+        <v>-0.4227</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.194</v>
+        <v>1.9403</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1344</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>1.9403</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1878</v>
+        <v>1.5828</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0595</v>
+        <v>0.9082</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1283</v>
+        <v>0.6747</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2821</v>
+        <v>1.3836</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2821</v>
+        <v>4.2358</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-2.8522</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4607</v>
+        <v>3.5407</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1615</v>
+        <v>0.8395</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6223</v>
+        <v>2.7012</v>
       </c>
       <c r="G17" t="n">
         <v>3.1581</v>
@@ -1780,13 +1780,13 @@
         <v>2.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3526</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2596</v>
+        <v>-0.2586</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9069</v>
+        <v>0.9859</v>
       </c>
       <c r="V17" t="n">
         <v>0.8194</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7924</v>
+        <v>1.0198</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3693</v>
+        <v>0.5695</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4231</v>
+        <v>0.4503</v>
       </c>
       <c r="G18" t="n">
         <v>0.6929</v>
@@ -1858,13 +1858,13 @@
         <v>0.3881</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0065</v>
+        <v>0.221</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3634</v>
+        <v>-0.1632</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3569</v>
+        <v>0.3842</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2821</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4998</v>
+        <v>0.4452</v>
       </c>
       <c r="E19" t="n">
         <v>0.6508</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.151</v>
+        <v>-0.2055</v>
       </c>
       <c r="G19" t="n">
         <v>0.4273</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0725</v>
+        <v>0.0179</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0606</v>
       </c>
       <c r="U19" t="n">
-        <v>0.133</v>
+        <v>0.0785</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. ABOUBACAR HIMA</t>
+          <t>C. KLOTZ MAROTO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3409</v>
+        <v>-0.1211</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4523</v>
+        <v>-1.46</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1114</v>
+        <v>1.3389</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1534</v>
+        <v>-2.5217</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-2.2426</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3938</v>
+        <v>-0.2791</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7685999999999999</v>
+        <v>-1.58</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.931</v>
+        <v>-1.5901</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1624</v>
+        <v>0.0101</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3848</v>
+        <v>-0.9417</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1714</v>
+        <v>-0.6525</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5561</v>
+        <v>-0.2892</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3881</v>
+        <v>2.1344</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3881</v>
+        <v>2.1344</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4244</v>
+        <v>0.1065</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3163</v>
+        <v>-0.1621</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1081</v>
+        <v>0.2686</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.1597</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1224</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. KLOTZ MAROTO</t>
+          <t>S. GACIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4031</v>
+        <v>-0.3083</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6602</v>
+        <v>-3.5302</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2571</v>
+        <v>3.2219</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.5217</v>
+        <v>1.7544</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.2426</v>
+        <v>-0.1887</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2791</v>
+        <v>1.9431</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.58</v>
+        <v>2.1124</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.5901</v>
+        <v>0.1359</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0101</v>
+        <v>1.9765</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9417</v>
+        <v>-0.358</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6525</v>
+        <v>-0.3246</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2892</v>
+        <v>-0.0334</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1344</v>
+        <v>-3.2985</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-6.015</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1344</v>
+        <v>2.7164</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1754</v>
+        <v>1.0762</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3623</v>
+        <v>-0.1918</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1869</v>
+        <v>1.268</v>
       </c>
       <c r="V21" t="n">
         <v>0.1597</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2821</v>
+        <v>0.5642</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1224</v>
+        <v>-0.4045</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. GACIC</t>
+          <t>S. ABOUBACAR HIMA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4333</v>
+        <v>-0.4532</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9306</v>
+        <v>-0.7526</v>
       </c>
       <c r="F22" t="n">
-        <v>3.4973</v>
+        <v>0.2994</v>
       </c>
       <c r="G22" t="n">
-        <v>1.7544</v>
+        <v>-1.1534</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1887</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9431</v>
+        <v>-0.3938</v>
       </c>
       <c r="J22" t="n">
-        <v>2.1124</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1359</v>
+        <v>-0.931</v>
       </c>
       <c r="L22" t="n">
-        <v>1.9765</v>
+        <v>0.1624</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.358</v>
+        <v>-0.3848</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3246</v>
+        <v>0.1714</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0334</v>
+        <v>-0.5561</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.2985</v>
+        <v>0.3881</v>
       </c>
       <c r="Q22" t="n">
-        <v>-6.015</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7164</v>
+        <v>0.3881</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.3121</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.016</v>
       </c>
       <c r="U22" t="n">
-        <v>1.5433</v>
+        <v>0.2961</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1597</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.4045</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. GARCIA BENITO</t>
+          <t>R. MARQUINA ROMERO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,40 +2203,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7768</v>
+        <v>-0.8598</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6867</v>
+        <v>-0.6267</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0901</v>
+        <v>-0.233</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3046</v>
+        <v>-0.9052</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5750999999999999</v>
+        <v>-0.4119</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8797</v>
+        <v>-0.4933</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2935</v>
+        <v>-0.6267</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0412</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3347</v>
+        <v>-0.6267</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0111</v>
+        <v>-0.2785</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5339</v>
+        <v>-0.4119</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.545</v>
+        <v>0.1335</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5278</v>
+        <v>0.0454</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6068</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.079</v>
+        <v>0.0454</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. MARQUINA ROMERO</t>
+          <t>I. GARCIA BENITO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,40 +2281,40 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.887</v>
+        <v>-0.9953</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6267</v>
+        <v>-0.987</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2603</v>
+        <v>-0.0083</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9052</v>
+        <v>-1.3046</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4119</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4933</v>
+        <v>-1.8797</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6267</v>
+        <v>-1.2935</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>0.0412</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6267</v>
+        <v>-1.3347</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2785</v>
+        <v>-0.0111</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4119</v>
+        <v>0.5339</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1335</v>
+        <v>-0.545</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0182</v>
+        <v>0.3093</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>0.3065</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0182</v>
+        <v>0.0028</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.075</v>
+        <v>-1.3692</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.2518</v>
+        <v>-1.6522</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1767</v>
+        <v>0.283</v>
       </c>
       <c r="G25" t="n">
         <v>-0.2807</v>
@@ -2404,13 +2404,13 @@
         <v>0.3881</v>
       </c>
       <c r="S25" t="n">
-        <v>0.952</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8008</v>
+        <v>0.4004</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1512</v>
+        <v>0.2574</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>13.9779</v>
+        <v>14.6452</v>
       </c>
       <c r="E26" t="n">
-        <v>3.4037</v>
+        <v>3.403799999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>10.5741</v>
+        <v>11.2415</v>
       </c>
       <c r="G26" t="n">
         <v>4.6992</v>
@@ -2452,13 +2452,13 @@
         <v>3.3367</v>
       </c>
       <c r="I26" t="n">
-        <v>1.362399999999999</v>
+        <v>1.3624</v>
       </c>
       <c r="J26" t="n">
-        <v>8.662399999999998</v>
+        <v>8.6624</v>
       </c>
       <c r="K26" t="n">
-        <v>5.0751</v>
+        <v>5.075099999999999</v>
       </c>
       <c r="L26" t="n">
         <v>3.587400000000001</v>
@@ -2482,13 +2482,13 @@
         <v>14.5525</v>
       </c>
       <c r="S26" t="n">
-        <v>5.7593</v>
+        <v>6.426600000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>0.7400000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="U26" t="n">
-        <v>5.019200000000001</v>
+        <v>5.686599999999999</v>
       </c>
       <c r="V26" t="n">
         <v>5.4597</v>
@@ -2497,7 +2497,7 @@
         <v>10.494</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.034399999999999</v>
+        <v>-5.0344</v>
       </c>
     </row>
   </sheetData>
